--- a/reports/Debug-purgatory-20260104/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/Week Total (Prior Year)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C9" s="2">
-        <v>2793</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>808</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,10 +563,10 @@
         <v>45657</v>
       </c>
       <c r="C11" s="2">
-        <v>122</v>
+        <v>313</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -577,10 +577,10 @@
         <v>45658</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2335</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -591,7 +591,7 @@
         <v>45659</v>
       </c>
       <c r="C13" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,7 +619,7 @@
         <v>45660</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>6</v>
@@ -633,10 +633,10 @@
         <v>45660</v>
       </c>
       <c r="C16" s="2">
-        <v>36</v>
+        <v>303</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C17" s="2">
-        <v>1871</v>
+        <v>1656</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>6</v>
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C19" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C20" s="2">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>6</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C21" s="2">
-        <v>6</v>
+        <v>851</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C22" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>6</v>
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C24" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>672</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>1965</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>6</v>
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C28" s="2">
-        <v>380</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45658</v>
+        <v>45656</v>
       </c>
       <c r="C29" s="2">
-        <v>684</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45658</v>
+        <v>45656</v>
       </c>
       <c r="C30" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45659</v>
+        <v>45657</v>
       </c>
       <c r="C31" s="2">
-        <v>72</v>
+        <v>1383</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>6</v>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C33" s="2">
-        <v>487</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C34" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>6</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
       <c r="C35" s="2">
-        <v>-3</v>
+        <v>19</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C36" s="2">
-        <v>22</v>
+        <v>1733</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>6</v>
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C37" s="2">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>6</v>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C39" s="2">
-        <v>311</v>
+        <v>130</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C40" s="2">
-        <v>2084</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45661</v>
+        <v>45656</v>
       </c>
       <c r="C41" s="2">
-        <v>25</v>
+        <v>-3</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>6</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C44" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C45" s="2">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C46" s="2">
-        <v>1125</v>
+        <v>2084</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>6</v>
@@ -1078,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C48" s="2">
-        <v>851</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45657</v>
+        <v>45662</v>
       </c>
       <c r="C49" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C50" s="2">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>6</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C52" s="2">
-        <v>672</v>
+        <v>1125</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C53" s="2">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C54" s="2">
-        <v>1965</v>
+        <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>6</v>
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45662</v>
+        <v>45657</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>6</v>
@@ -1190,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C56" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>6</v>
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C57" s="2">
-        <v>808</v>
+        <v>2</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C58" s="2">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1235,10 +1235,10 @@
         <v>45658</v>
       </c>
       <c r="C59" s="2">
-        <v>2335</v>
+        <v>380</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C60" s="2">
-        <v>38</v>
+        <v>684</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C61" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C62" s="2">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>6</v>
@@ -1291,10 +1291,10 @@
         <v>45660</v>
       </c>
       <c r="C63" s="2">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1305,10 +1305,10 @@
         <v>45661</v>
       </c>
       <c r="C64" s="2">
-        <v>1656</v>
+        <v>487</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>45662</v>
       </c>
       <c r="C65" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>6</v>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45662</v>
+        <v>45656</v>
       </c>
       <c r="C66" s="2">
-        <v>18</v>
+        <v>1215</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>6</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C67" s="2">
-        <v>1215</v>
+        <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>6</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C68" s="2">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>6</v>
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C69" s="2">
-        <v>12</v>
+        <v>712</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1389,10 +1389,10 @@
         <v>45659</v>
       </c>
       <c r="C70" s="2">
-        <v>712</v>
+        <v>1567</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1403,7 +1403,7 @@
         <v>45659</v>
       </c>
       <c r="C71" s="2">
-        <v>1567</v>
+        <v>3</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>6</v>
@@ -1417,7 +1417,7 @@
         <v>45659</v>
       </c>
       <c r="C72" s="2">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>6</v>
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C73" s="2">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>6</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C74" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>6</v>
@@ -1459,7 +1459,7 @@
         <v>45661</v>
       </c>
       <c r="C75" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>6</v>
@@ -1470,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C76" s="2">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1487,10 +1487,10 @@
         <v>45662</v>
       </c>
       <c r="C77" s="2">
-        <v>288</v>
+        <v>2295</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1501,7 +1501,7 @@
         <v>45662</v>
       </c>
       <c r="C78" s="2">
-        <v>2295</v>
+        <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>6</v>
@@ -1515,7 +1515,7 @@
         <v>45662</v>
       </c>
       <c r="C79" s="2">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>6</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45662</v>
+        <v>45657</v>
       </c>
       <c r="C80" s="2">
-        <v>83</v>
+        <v>2793</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>6</v>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C82" s="2">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>6</v>
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C83" s="2">
-        <v>1383</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>6</v>
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C84" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>6</v>
@@ -1596,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>6</v>
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C86" s="2">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>6</v>
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C87" s="2">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>6</v>
@@ -1641,10 +1641,10 @@
         <v>45660</v>
       </c>
       <c r="C88" s="2">
-        <v>1733</v>
+        <v>1871</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C89" s="2">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>6</v>
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>6</v>
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C91" s="2">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>6</v>
@@ -1694,13 +1694,13 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C92" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
